--- a/Result/checksun_type/紙漿、紙類原料.xlsx
+++ b/Result/checksun_type/紙漿、紙類原料.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>37.83</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>38.31</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>38.31</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>3869358.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>3871172.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>3871172.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>8979574.0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>5956371.06</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>5956371.06</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-403343.9373719934</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>3869358</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>3869358.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>37.57</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>37.91</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>38.32</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>38.32</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2932934.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>5085370.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>5085370.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>8966073.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>6139245.96</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>6139245.96</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-248911.3340451708</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2932934</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2932934.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>37.38</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>37.93</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>38.33</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>38.33</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>3235720.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>8975058.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>8975058.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>8982585.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>6206365.46</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>6206365.46</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>80927.50406618882</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>3235720</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>3235720.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>37.33</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>37.97</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>38.34</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>38.34</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>3269719.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>9730531.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>9730531.199999999</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>8809203.3</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>6279424.88</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>6279424.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>516794.2190800523</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>3269719</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>3269719.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>37.43</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>38.04</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>38.36</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>38.04</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>38.36</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>6048132.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>10499888.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>10499888</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>8611623.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>6343834.52</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>6343834.52</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>1117361.268418428</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>6048132</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>6048132.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>37.59</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>38.39</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>38.39</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>9940349.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>14087975.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>14087975.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>8293851.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>6415232.58</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>6415232.58</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>1637721.329315448</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>9940349</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>9940349.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>37.79</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>38.19</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>38.43</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>38.43</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>22381373.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>12846776.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>12846776.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>7660367.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>6365776.64</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>6365776.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>1905579.547407068</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>22381373</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>22381373.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>37.95</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>38.26</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>38.47</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>38.47</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>7013083.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>8990112.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>8990112.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>6268708.0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>6009271.5</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>6009271.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>887210.8751305575</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>7013083</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>7013083.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>38.01</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>38.3</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>38.48</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>38.48</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>7116503.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>7887875.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>7887875.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>6092590.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>6064102.26</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>6064102.26</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>1047314.88348088</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>7116503</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>7116503.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>38.02</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>38.32</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>38.5</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>38.32</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>38.5</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>23988569.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>6723359.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>6723359.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>5736961.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>6104545.72</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>6104545.72</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>1227550.078142742</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>23988569</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>23988569.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>38.04</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>38.34</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>38.52</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>38.52</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>3734356.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>2499727.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>2499727.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>3608565.8</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>5703808.76</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>5703808.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-366533.5037025558</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>3734356</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>3734356.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>10.2</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>9.84</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>9.89</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>9.890000000000001</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>31062132.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>23321241.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>23321241.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>43900128.9</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>24044594.92</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>24044594.92</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>186860.3581370898</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>31062132</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>31062132.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>10.17</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>9.81</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>9.88</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>9.880000000000001</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>27731975.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>24453306.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>24453306</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>42732270.8</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>23734277.84</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>23734277.84</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>394433.1788898893</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>27731975</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>27731975.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>10.19</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>9.89</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>9.890000000000001</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>20424768.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>35321007.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>35321007.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>40764519.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>23359953.88</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>23359953.88</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>1033681.416433543</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>20424768</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>20424768.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>10.25</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>9.77</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>9.88</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>9.880000000000001</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>22401539.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>52798715.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>52798715.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>39713960.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>23096481.4</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>23096481.4</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>2692891.026623271</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>22401539</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>22401539.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>10.23</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>9.77</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>9.88</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>9.880000000000001</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>14985792.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>63733974.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>63733974.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>38551362.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>22873765.1</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>22873765.1</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>4755218.89737206</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>14985792</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>14985792.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>10.166</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>9.75</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>9.88</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>9.880000000000001</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>36722456.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>64479016.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>64479016.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>38635712.4</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>23049141.46</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>23049141.46</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>8326116.644964188</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>36722456</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>36722456.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>10.098</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>9.73</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>9.89</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>9.890000000000001</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>82070483.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>61011235.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>61011235.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>36198689.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>23309656.7</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>23309656.7</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>10801109.54706135</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>82070483</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>82070483.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>9.976</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>9.71</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>9.88</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>9.880000000000001</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>107813308.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>46208032.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>46208032.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>29798120.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>22370621.78</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>22370621.78</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>9092342.60194797</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>107813308</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>107813308.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>9.762</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>9.67</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>9.88</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>9.880000000000001</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>77077834.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>26629205.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>26629205</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>20430638.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>20694301.92</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>20694301.92</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>3568360.623144995</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>77077834</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>77077834.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>9.672</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>9.66</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>9.87</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>9.869999999999999</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>18711002.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>13368750.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>13368750.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>15012229.6</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>19554421.34</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>19554421.34</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-1157397.154542999</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>18711002</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>18711002.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>9.626</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>9.66</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>9.88</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>9.880000000000001</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>19383551.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>12792408.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>12792408.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>15568578.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>19429279.5</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>19429279.5</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-1613554.938577883</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>19383551</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>19383551.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>11.8</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>12.14</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>12.15</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>18005548.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>19177580.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>19177580.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>29580981.1</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>22421239.98</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>22421239.98</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-1785117.168213371</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>18005548</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>18005548.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,21 +10947,17 @@
           <t>11.71</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AM25" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="AO25" t="inlineStr">
         <is>
           <t>12.17</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>12.16</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>12.17</t>
-        </is>
-      </c>
       <c r="AP25" t="inlineStr">
         <is>
           <t>-186.05</t>
@@ -11140,20 +10998,16 @@
           <t>7727015.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>21268995.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>21268995.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>30374102.1</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>22678426.12</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>22678426.12</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-1555011.203350872</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>7727015</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>7727015.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,21 +11377,17 @@
           <t>11.74</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>12.22</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
+      <c r="AM26" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="AO26" t="inlineStr">
         <is>
           <t>12.18</t>
         </is>
       </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>12.18</t>
-        </is>
-      </c>
       <c r="AP26" t="inlineStr">
         <is>
           <t>-383.32</t>
@@ -11576,20 +11428,16 @@
           <t>18977250.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>27449635.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>27449635.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>30912071.6</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>23124120.4</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>23124120.4</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-69480.88914190978</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>18977250</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>18977250.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>11.9</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>12.28</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>12.19</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>12.19</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>20356352.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>32034183.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>32034183.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>30173949.8</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>23085176.4</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>23085176.4</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>849804.4129116759</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>20356352</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>20356352.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>12.18</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>12.2</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>30821738.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>41658482.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>41658482.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>29511896.2</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>23187205.66</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>23187205.66</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>1984958.043955665</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>30821738</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>30821738.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>12.35</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>12.4</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>12.22</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>12.22</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>28462621.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>39984381.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>39984381.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>27721210.7</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>22822287.78</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>22822287.78</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>2414423.37244866</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>28462621</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>28462621.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>12.52</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>12.42</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>12.23</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>12.23</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>38630216.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>39479209.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>39479209</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>26345598.1</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>22740925.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>22740925</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>3194478.399851203</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>38630216</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>38630216.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>12.54</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>12.23</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>12.23</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>41899989.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>34374507.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>34374507.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>25719252.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>22198404.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>22198404</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>3105369.03186015</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>41899989</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>41899989.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>12.4</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>12.44</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>12.22</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>12.22</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>68477848.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>28313716.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>28313716.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>23284004.4</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>21757255.78</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>21757255.78</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>2516831.076449357</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>68477848</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>68477848.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>12.23</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>12.38</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>12.2</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>22451234.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>17365310.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>17365310</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>18118301.0</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>20655784.36</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>20655784.36</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-1261452.005439252</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>22451234</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>22451234.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>12.17</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>12.34</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>12.19</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>12.19</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>25936758.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>15458039.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>15458039.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>18385630.8</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>20507029.94</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>20507029.94</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-1682524.479371578</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>25936758</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>25936758.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>18.12</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>17.64</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>17.64</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>6791803.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>10058420.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>10058420.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>20353292.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>15094194.92</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>15094194.92</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-1996695.871977523</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>6791803</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>6791803.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>18.02</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>17.75</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>17.63</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>17.63</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>5688835.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>12748490.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>12748490.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>23731866.1</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>15360881.76</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>15360881.76</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-1408807.419375379</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>5688835</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>5688835.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>17.99</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>17.7</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>16688578.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>15079634.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>15079634.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>25532824.5</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>15494092.0</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>15494092</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-400477.0792517662</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>16688578</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>16688578.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>18.07</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>11811096.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>17474774.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>17474774.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>25895143.3</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>15509598.64</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>15509598.64</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-124246.3048161827</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>11811096</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>11811096.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>18.25</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>17.63</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>9311790.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>28417473.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>28417473</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>26672932.2</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>15411366.58</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>15411366.58</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>797393.8124066554</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>9311790</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>9311790.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>18.33</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>20242154.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>30648164.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>30648164.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>26970051.1</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>15411161.88</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>15411161.88</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>2353326.986567616</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>20242154</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>20242154.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>18.4</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>17.58</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>17344555.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>34715241.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>34715241.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>26279480.7</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>15172436.36</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>15172436.36</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>3320930.842991576</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>17344555</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>17344555.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>18.37</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>17.54</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>28664279.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>35986014.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>35986014.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>26734953.5</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>14965321.98</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>14965321.98</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>4895074.429204676</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>28664279</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>28664279.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>18.17</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>17.48</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>17.6</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>66524587.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>34315511.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>34315511.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>25013118.4</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>14532416.86</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>14532416.86</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>5756199.32275179</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>66524587</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>66524587.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>17.91</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>17.42</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>17.57</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>17.57</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>20465247.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>24928391.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>24928391.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>19851734.8</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>13542466.52</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>13542466.52</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>2724337.623435102</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>20465247</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>20465247.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>17.72</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>17.38</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>17.56</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>17.56</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>40577540.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>23291937.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>23291937.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>18777885.8</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>13347392.76</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>13347392.76</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>3230738.137860011</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>40577540</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>40577540.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
